--- a/docs/Data_Dictionary.xlsx
+++ b/docs/Data_Dictionary.xlsx
@@ -8,13 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/iris/Documents/GitHub/Intelligent-Blood-Presure-Risk-Assessment/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0C0D6F1-F4CF-7948-B132-0941C7FDB33B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C8D9C8-55EE-934F-9B5B-CFD119B31421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="17160" xr2:uid="{21C54988-1E31-4D4A-B0C4-34B7D059BE07}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Variable" sheetId="1" r:id="rId1"/>
+    <sheet name="Reference" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="Data_Type_List">Reference!$A$15:$A$18</definedName>
+    <definedName name="Dataset_List">Reference!$A$21:$A$26</definedName>
+    <definedName name="ML_Role_List">Reference!$A$2:$A$7</definedName>
+    <definedName name="Source_Dataset_List">Reference!$A$21:$A$26</definedName>
+    <definedName name="Status_List">Reference!$A$10:$A$12</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,10 +46,357 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="102">
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Data Type</t>
+  </si>
+  <si>
+    <t>Unit / Values</t>
+  </si>
+  <si>
+    <t>Source Dataset</t>
+  </si>
+  <si>
+    <t>ML Role</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>Decision Ref</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>SEQN</t>
+  </si>
+  <si>
+    <t>Unique participant identifier</t>
+  </si>
+  <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>Unique ID</t>
+  </si>
+  <si>
+    <t>DEMO</t>
+  </si>
+  <si>
+    <t>Primary Key</t>
+  </si>
+  <si>
+    <t>DE003</t>
+  </si>
+  <si>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>Used only to merge datasets. Never used as a machine learning feature.</t>
+  </si>
+  <si>
+    <t>Version 1</t>
+  </si>
+  <si>
+    <t>RIDAGEYR</t>
+  </si>
+  <si>
+    <t>Age at examination</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Predictor</t>
+  </si>
+  <si>
+    <t>B002</t>
+  </si>
+  <si>
+    <t>Age in completed years at the time of examination.</t>
+  </si>
+  <si>
+    <t>RIAGENDR</t>
+  </si>
+  <si>
+    <t>Biological sex</t>
+  </si>
+  <si>
+    <t>Categorical</t>
+  </si>
+  <si>
+    <t>B003</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Verify coding from the official NHANES documentation before interpretation.</t>
+  </si>
+  <si>
+    <t>BMXBMI</t>
+  </si>
+  <si>
+    <t>Body Mass Index</t>
+  </si>
+  <si>
+    <t>kg/m²</t>
+  </si>
+  <si>
+    <t>BMX</t>
+  </si>
+  <si>
+    <t>B004</t>
+  </si>
+  <si>
+    <t>Measured BMI provided by NHANES.</t>
+  </si>
+  <si>
+    <t>BPXOSY1</t>
+  </si>
+  <si>
+    <t>First systolic blood pressure reading</t>
+  </si>
+  <si>
+    <t>mmHg</t>
+  </si>
+  <si>
+    <t>BPXO</t>
+  </si>
+  <si>
+    <t>Intermediate</t>
+  </si>
+  <si>
+    <t>FE001</t>
+  </si>
+  <si>
+    <t>Used to calculate Average_SBP.</t>
+  </si>
+  <si>
+    <t>BPXOSY2</t>
+  </si>
+  <si>
+    <t>Second systolic blood pressure reading</t>
+  </si>
+  <si>
+    <t>BPXOSY3</t>
+  </si>
+  <si>
+    <t>Third systolic blood pressure reading</t>
+  </si>
+  <si>
+    <t>BPXODI1</t>
+  </si>
+  <si>
+    <t>First diastolic blood pressure reading</t>
+  </si>
+  <si>
+    <t>FE002</t>
+  </si>
+  <si>
+    <t>Used to calculate Average_DBP.</t>
+  </si>
+  <si>
+    <t>BPXODI2</t>
+  </si>
+  <si>
+    <t>Second diastolic blood pressure reading</t>
+  </si>
+  <si>
+    <t>BPXODI3</t>
+  </si>
+  <si>
+    <t>Third diastolic blood pressure reading</t>
+  </si>
+  <si>
+    <t>Average_SBP</t>
+  </si>
+  <si>
+    <t>Average systolic blood pressure</t>
+  </si>
+  <si>
+    <t>Engineered</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Arithmetic mean of all available systolic blood pressure measurements.</t>
+  </si>
+  <si>
+    <t>Average_DBP</t>
+  </si>
+  <si>
+    <t>Average diastolic blood pressure</t>
+  </si>
+  <si>
+    <t>Engineered Feature</t>
+  </si>
+  <si>
+    <t>Arithmetic mean of all available diastolic blood pressure measurements.</t>
+  </si>
+  <si>
+    <t>BPQ050A</t>
+  </si>
+  <si>
+    <t>Blood pressure medication use</t>
+  </si>
+  <si>
+    <t>BPQ</t>
+  </si>
+  <si>
+    <t>B005</t>
+  </si>
+  <si>
+    <t>Verify response coding using the NHANES documentation.</t>
+  </si>
+  <si>
+    <t>DIQ010</t>
+  </si>
+  <si>
+    <t>Diabetes diagnosis</t>
+  </si>
+  <si>
+    <t>DIQ</t>
+  </si>
+  <si>
+    <t>B006</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Unique identifier used to merge datasets. Never used as a machine learning feature.</t>
+  </si>
+  <si>
+    <t>Input variable used by the machine learning model to predict the target.</t>
+  </si>
+  <si>
+    <t>Variable the model is trained to predict.</t>
+  </si>
+  <si>
+    <t>Variable used to create another feature. Not used directly for model training.</t>
+  </si>
+  <si>
+    <t>Variable created from one or more existing variables through feature engineering.</t>
+  </si>
+  <si>
+    <t>Excluded</t>
+  </si>
+  <si>
+    <t>Variable intentionally excluded from model training but retained in the working dataset or documentation.</t>
+  </si>
+  <si>
+    <t>Information has not yet been verified from the official NHANES documentation.</t>
+  </si>
+  <si>
+    <t>Information has been confirmed using the official NHANES documentation or project decisions.</t>
+  </si>
+  <si>
+    <t>Deprecated</t>
+  </si>
+  <si>
+    <t>No longer used in the project but retained for historical reference.</t>
+  </si>
+  <si>
+    <t>Unique value used to identify each participant.</t>
+  </si>
+  <si>
+    <t>Numeric value measured on a continuous scale.</t>
+  </si>
+  <si>
+    <t>Variable containing discrete categories or coded values.</t>
+  </si>
+  <si>
+    <t>Boolean</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">True/False or Yes/No variable. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Not currently used in Version 1 but included for completeness.)</t>
+    </r>
+  </si>
+  <si>
+    <t>NHANES Demographics</t>
+  </si>
+  <si>
+    <t>NHANES Body Measures</t>
+  </si>
+  <si>
+    <t>NHANES Blood Pressure Examination</t>
+  </si>
+  <si>
+    <t>NHANES Blood Pressure Questionnaire</t>
+  </si>
+  <si>
+    <t>NHANES Diabetes Questionnaire</t>
+  </si>
+  <si>
+    <t>Variable created during this project.</t>
+  </si>
+  <si>
+    <t>Yes (1) / No (2)</t>
+  </si>
+  <si>
+    <t>Male (1) / Female (2)</t>
+  </si>
+  <si>
+    <t>Yes (1) / No (2) / Borderline (3)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -69,13 +424,65 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -86,6 +493,25 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AEFEA6B8-560E-A14C-B0C2-931FD9332DFB}" name="Table1" displayName="Table1" ref="A1:J4" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J4" xr:uid="{AEFEA6B8-560E-A14C-B0C2-931FD9332DFB}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{3E361EE4-5B9B-3F42-A4DD-2E8450125279}" name="Variable" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{7C9C7F16-FBFD-A642-8AD1-8A3C749052AA}" name="Description" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{5F1DB7E0-8581-9E44-834B-BC86371D0915}" name="Data Type" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{6B49D89D-8A38-DA4F-A6A3-829504247A67}" name="Unit / Values" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{09215567-59F0-3F41-8419-B10E3504C6AF}" name="Source Dataset" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{13D2DBD4-3AE9-D04C-947A-338727E6A369}" name="ML Role" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{9724DB8A-4F29-DA44-9380-5375023563C1}" name="Version" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{519D5D21-318D-C749-9231-DD41A0896D34}" name="Decision Ref" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{73B0B7EE-94C8-5643-9AC1-323256C4C30B}" name="Status" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{E3E46436-7F1F-D340-AFE1-B7E234FEC110}" name="Notes" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -405,9 +831,716 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58F8B548-0862-6A41-948F-C1322BD6B13C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="63.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F15" xr:uid="{C2F7D46E-B5C2-C841-A400-CEFA8F3928FA}">
+      <formula1>ML_Role_List</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E15" xr:uid="{49C639EC-6868-844C-AF36-B6645B7D5438}">
+      <formula1>Dataset_List</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I15" xr:uid="{65108AD6-221A-4344-B59B-3974109E0A62}">
+      <formula1>Status_List</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8737D505-623D-2548-B3E7-C9447C1B1481}">
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="87.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>